--- a/Analysis/Heatmaps_Spearman_Correlation/Data/Output_TB_TF_venn/common_models_md_20.xlsx
+++ b/Analysis/Heatmaps_Spearman_Correlation/Data/Output_TB_TF_venn/common_models_md_20.xlsx
@@ -19,52 +19,52 @@
     <t>File name</t>
   </si>
   <si>
+    <t>0_8AFI_TF</t>
+  </si>
+  <si>
+    <t>0_7Y9C_TB</t>
+  </si>
+  <si>
+    <t>1_7Y9C_TB</t>
+  </si>
+  <si>
+    <t>4_8EQ5_TF</t>
+  </si>
+  <si>
+    <t>0_7UDK_TF</t>
+  </si>
+  <si>
+    <t>0_8AFI_TB</t>
+  </si>
+  <si>
+    <t>6_7UDK_TB</t>
+  </si>
+  <si>
+    <t>8_7XV1_TB</t>
+  </si>
+  <si>
+    <t>8_7XV1_TF</t>
+  </si>
+  <si>
+    <t>1_7Y9C_TF</t>
+  </si>
+  <si>
+    <t>0_7Y9C_TF</t>
+  </si>
+  <si>
+    <t>2_7ZX4_TF</t>
+  </si>
+  <si>
+    <t>4_8EQ5_TB</t>
+  </si>
+  <si>
     <t>6_7UDK_TF</t>
   </si>
   <si>
+    <t>0_7UDK_TB</t>
+  </si>
+  <si>
     <t>2_7ZX4_TB</t>
-  </si>
-  <si>
-    <t>8_7XV1_TF</t>
-  </si>
-  <si>
-    <t>1_7Y9C_TF</t>
-  </si>
-  <si>
-    <t>0_8AFI_TB</t>
-  </si>
-  <si>
-    <t>4_8EQ5_TB</t>
-  </si>
-  <si>
-    <t>0_7UDK_TB</t>
-  </si>
-  <si>
-    <t>1_7Y9C_TB</t>
-  </si>
-  <si>
-    <t>6_7UDK_TB</t>
-  </si>
-  <si>
-    <t>0_7Y9C_TB</t>
-  </si>
-  <si>
-    <t>0_7UDK_TF</t>
-  </si>
-  <si>
-    <t>0_8AFI_TF</t>
-  </si>
-  <si>
-    <t>4_8EQ5_TF</t>
-  </si>
-  <si>
-    <t>8_7XV1_TB</t>
-  </si>
-  <si>
-    <t>2_7ZX4_TF</t>
-  </si>
-  <si>
-    <t>0_7Y9C_TF</t>
   </si>
 </sst>
 </file>
